--- a/4_outputs/final/Table30.xlsx
+++ b/4_outputs/final/Table30.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -430,7 +430,7 @@
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Raw gap</t>
+          <t>Semantic Gap</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Reg. Comp.</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H1b. Policy--research dominance Semantic gap</t>
+          <t>H1b. Research--policy dominance Semantic gap</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
